--- a/trade_journal.xlsx
+++ b/trade_journal.xlsx
@@ -882,7 +882,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>VYM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -896,39 +896,47 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>291.365</v>
-      </c>
-      <c r="F10" t="n">
-        <v>71.3</v>
+        <v>164.5402</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>2026-07-31T16:08:56+00:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>2026-09-11T13:35:24.747298+00:00</t>
         </is>
       </c>
+      <c r="J10" t="n">
+        <v>163.275</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-9.775000000000006</v>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>increase toward target 19% of capital (core)</t>
+          <t>backfilled from Tiger fill history</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>satellite</t>
+          <t>core</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -937,13 +945,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>101.8016666666667</v>
+        <v>289.695</v>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
+        <v>71.3</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -952,15 +960,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-20T14:00:21.620784+00:00</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>-59.90500000000002</v>
+          <t>2026-09-11T13:35:24.747298+00:00</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>increase toward target 21% of capital (satellite)</t>
+          <t>increase toward target 19% of capital (core)</t>
         </is>
       </c>
     </row>
@@ -981,10 +986,10 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>229.24</v>
+        <v>224.6039</v>
       </c>
       <c r="F12" t="n">
         <v>99.7</v>
@@ -1011,12 +1016,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VYM</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>satellite</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1025,10 +1030,13 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>164.5402</v>
+        <v>101.8016666666667</v>
+      </c>
+      <c r="F13" t="n">
+        <v>100</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1037,23 +1045,23 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-07-31T16:08:56+00:00</t>
+          <t>2026-08-20T14:00:21.620784+00:00</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-09-11T13:35:24.747298+00:00</t>
+          <t>2026-09-14T13:35:23.909758+00:00</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>163.275</v>
+        <v>84.2212</v>
       </c>
       <c r="K13" t="n">
-        <v>-9.775000000000006</v>
+        <v>-165.3878000000001</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>backfilled from Tiger fill history</t>
+          <t>increase toward target 21% of capital (satellite)</t>
         </is>
       </c>
     </row>

--- a/trade_journal.xlsx
+++ b/trade_journal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -972,7 +972,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -986,26 +986,34 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>224.6039</v>
+        <v>101.8016666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-09-10T13:35:22.777452+00:00</t>
-        </is>
+          <t>2026-08-20T14:00:21.620784+00:00</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-14T13:35:23.909758+00:00</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>84.2212</v>
       </c>
       <c r="K12" t="n">
-        <v>3.22999999999999</v>
+        <v>-165.3878000000001</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1030,36 +1038,118 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>101.8016666666667</v>
+        <v>87.02</v>
       </c>
       <c r="F13" t="n">
         <v>100</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-09-15T13:35:23.136618+00:00</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>increase toward target 21% of capital (satellite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>satellite</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>505.92</v>
+      </c>
+      <c r="F14" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-09-15T13:35:23.136618+00:00</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>increase toward target 21% of capital (satellite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>satellite</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>224.6039</v>
+      </c>
+      <c r="F15" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-08-20T14:00:21.620784+00:00</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-09-14T13:35:23.909758+00:00</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>84.2212</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-165.3878000000001</v>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-10T13:35:22.777452+00:00</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-15T13:35:23.136618+00:00</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>225.695</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6.50330000000011</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>increase toward target 21% of capital (satellite)</t>
         </is>

--- a/trade_journal.xlsx
+++ b/trade_journal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -745,12 +745,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>satellite</t>
+          <t>core</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -759,13 +759,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>298.57</v>
+        <v>188.9875</v>
       </c>
       <c r="F7" t="n">
-        <v>99.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -774,24 +774,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:24.352592+00:00</t>
-        </is>
+          <t>2026-08-12T14:13:57.782108+00:00</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>-9.382500000000022</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>increase toward target 21% of capital (satellite)</t>
+          <t>increase toward target 18% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>satellite</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -800,42 +803,50 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>188.9875</v>
+        <v>514.5</v>
       </c>
       <c r="F8" t="n">
-        <v>76.2</v>
+        <v>99.7</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-12T14:13:57.782108+00:00</t>
-        </is>
+          <t>2026-09-09T13:35:24.352592+00:00</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-10T13:35:22.777452+00:00</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>509.365</v>
       </c>
       <c r="K8" t="n">
-        <v>-9.382500000000022</v>
+        <v>-5.134999999999991</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>increase toward target 18% of capital (core)</t>
+          <t>increase toward target 21% of capital (satellite)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>VYM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>satellite</t>
+          <t>core</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -844,13 +855,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
-        <v>514.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>99.7</v>
+        <v>164.5402</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -859,30 +867,30 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:24.352592+00:00</t>
+          <t>2026-07-31T16:08:56+00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-10T13:35:22.777452+00:00</t>
+          <t>2026-09-11T13:35:24.747298+00:00</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>509.365</v>
+        <v>163.275</v>
       </c>
       <c r="K9" t="n">
-        <v>-5.134999999999991</v>
+        <v>-9.775000000000006</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>increase toward target 21% of capital (satellite)</t>
+          <t>backfilled from Tiger fill history</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>VYM</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -896,47 +904,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>164.5402</v>
+        <v>289.695</v>
+      </c>
+      <c r="F10" t="n">
+        <v>71.3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-07-31T16:08:56+00:00</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
           <t>2026-09-11T13:35:24.747298+00:00</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>163.275</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-9.775000000000006</v>
-      </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>backfilled from Tiger fill history</t>
+          <t>increase toward target 19% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>satellite</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -945,27 +945,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>289.695</v>
+        <v>101.8016666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>71.3</v>
+        <v>100</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-11T13:35:24.747298+00:00</t>
-        </is>
+          <t>2026-08-20T14:00:21.620784+00:00</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-14T13:35:23.909758+00:00</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>84.2212</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-165.3878000000001</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>increase toward target 19% of capital (core)</t>
+          <t>increase toward target 21% of capital (satellite)</t>
         </is>
       </c>
     </row>
@@ -986,34 +997,23 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
-        <v>101.8016666666667</v>
+        <v>87.02</v>
       </c>
       <c r="F12" t="n">
         <v>100</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-20T14:00:21.620784+00:00</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-09-14T13:35:23.909758+00:00</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>84.2212</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-165.3878000000001</v>
+          <t>2026-09-15T13:35:23.136618+00:00</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1038,23 +1038,34 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>87.02</v>
+        <v>224.6039</v>
       </c>
       <c r="F13" t="n">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>2026-09-10T13:35:22.777452+00:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>2026-09-15T13:35:23.136618+00:00</t>
         </is>
+      </c>
+      <c r="J13" t="n">
+        <v>225.695</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.50330000000011</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1065,7 +1076,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1079,13 +1090,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>505.92</v>
+        <v>157.49</v>
       </c>
       <c r="F14" t="n">
-        <v>99.8</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1094,7 +1105,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-15T13:35:23.136618+00:00</t>
+          <t>2026-09-16T13:35:24.965917+00:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1123,33 +1134,126 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>224.6039</v>
+        <v>226.705</v>
       </c>
       <c r="F15" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-09-16T13:35:24.965917+00:00</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>increase toward target 21% of capital (satellite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>satellite</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>298.57</v>
+      </c>
+      <c r="F16" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-09-10T13:35:22.777452+00:00</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-09T13:35:24.352592+00:00</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-16T13:35:24.965917+00:00</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>258.955</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-79.23000000000002</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>increase toward target 21% of capital (satellite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>satellite</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>505.92</v>
+      </c>
+      <c r="F17" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>2026-09-15T13:35:23.136618+00:00</t>
         </is>
       </c>
-      <c r="J15" t="n">
-        <v>225.695</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6.50330000000011</v>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-16T13:35:24.965917+00:00</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>518.8150000000001</v>
+      </c>
+      <c r="K17" t="n">
+        <v>12.89500000000004</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>increase toward target 21% of capital (satellite)</t>
         </is>

--- a/trade_journal.xlsx
+++ b/trade_journal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -745,12 +745,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>satellite</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -759,42 +759,50 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>188.9875</v>
+        <v>514.5</v>
       </c>
       <c r="F7" t="n">
-        <v>76.2</v>
+        <v>99.7</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-12T14:13:57.782108+00:00</t>
-        </is>
+          <t>2026-09-09T13:35:24.352592+00:00</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-10T13:35:22.777452+00:00</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>509.365</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.382500000000022</v>
+        <v>-5.134999999999991</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>increase toward target 18% of capital (core)</t>
+          <t>increase toward target 21% of capital (satellite)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>VYM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>satellite</t>
+          <t>core</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -803,13 +811,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>514.5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>99.7</v>
+        <v>164.5402</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -818,35 +823,35 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:24.352592+00:00</t>
+          <t>2026-07-31T16:08:56+00:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-09-10T13:35:22.777452+00:00</t>
+          <t>2026-09-11T13:35:24.747298+00:00</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>509.365</v>
+        <v>163.275</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.134999999999991</v>
+        <v>-9.775000000000006</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>increase toward target 21% of capital (satellite)</t>
+          <t>backfilled from Tiger fill history</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VYM</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>satellite</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -855,10 +860,13 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>164.5402</v>
+        <v>101.8016666666667</v>
+      </c>
+      <c r="F9" t="n">
+        <v>100</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -867,35 +875,35 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-07-31T16:08:56+00:00</t>
+          <t>2026-08-20T14:00:21.620784+00:00</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-09-11T13:35:24.747298+00:00</t>
+          <t>2026-09-14T13:35:23.909758+00:00</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>163.275</v>
+        <v>84.2212</v>
       </c>
       <c r="K9" t="n">
-        <v>-9.775000000000006</v>
+        <v>-165.3878000000001</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>backfilled from Tiger fill history</t>
+          <t>increase toward target 21% of capital (satellite)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>satellite</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -904,34 +912,45 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>289.695</v>
+        <v>224.6039</v>
       </c>
       <c r="F10" t="n">
-        <v>71.3</v>
+        <v>99.7</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-09-11T13:35:24.747298+00:00</t>
-        </is>
+          <t>2026-09-10T13:35:22.777452+00:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-15T13:35:23.136618+00:00</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>225.695</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.50330000000011</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>increase toward target 19% of capital (core)</t>
+          <t>increase toward target 21% of capital (satellite)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -945,13 +964,13 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>101.8016666666667</v>
+        <v>298.57</v>
       </c>
       <c r="F11" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -960,19 +979,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-20T14:00:21.620784+00:00</t>
+          <t>2026-09-09T13:35:24.352592+00:00</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-09-14T13:35:23.909758+00:00</t>
+          <t>2026-09-16T13:35:24.965917+00:00</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>84.2212</v>
+        <v>258.955</v>
       </c>
       <c r="K11" t="n">
-        <v>-165.3878000000001</v>
+        <v>-79.23000000000002</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -983,7 +1002,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -997,23 +1016,34 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>87.02</v>
+        <v>505.92</v>
       </c>
       <c r="F12" t="n">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>2026-09-15T13:35:23.136618+00:00</t>
         </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-16T13:35:24.965917+00:00</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>518.8150000000001</v>
+      </c>
+      <c r="K12" t="n">
+        <v>12.89500000000004</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1024,12 +1054,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>satellite</t>
+          <t>core</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1038,50 +1068,42 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>224.6039</v>
+        <v>188.9875</v>
       </c>
       <c r="F13" t="n">
-        <v>99.7</v>
+        <v>76.2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-09-10T13:35:22.777452+00:00</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-09-15T13:35:23.136618+00:00</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>225.695</v>
+          <t>2026-08-12T14:13:57.782108+00:00</t>
+        </is>
       </c>
       <c r="K13" t="n">
-        <v>6.50330000000011</v>
+        <v>-11.61000000000004</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>increase toward target 21% of capital (satellite)</t>
+          <t>increase toward target 18% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>satellite</t>
+          <t>core</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1090,13 +1112,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>157.49</v>
+        <v>289.695</v>
       </c>
       <c r="F14" t="n">
-        <v>99.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1105,19 +1127,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-16T13:35:24.965917+00:00</t>
-        </is>
+          <t>2026-09-11T13:35:24.747298+00:00</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>-2.464999999999975</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>increase toward target 21% of capital (satellite)</t>
+          <t>increase toward target 19% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1131,13 +1156,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>226.705</v>
+        <v>87.02</v>
       </c>
       <c r="F15" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1146,8 +1171,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-16T13:35:24.965917+00:00</t>
-        </is>
+          <t>2026-09-15T13:35:23.136618+00:00</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>1.570000000000022</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1158,7 +1186,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1175,31 +1203,23 @@
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>298.57</v>
+        <v>226.705</v>
       </c>
       <c r="F16" t="n">
-        <v>99.90000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-09T13:35:24.352592+00:00</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
           <t>2026-09-16T13:35:24.965917+00:00</t>
         </is>
       </c>
-      <c r="J16" t="n">
-        <v>258.955</v>
-      </c>
       <c r="K16" t="n">
-        <v>-79.23000000000002</v>
+        <v>17.16499999999999</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1227,33 +1247,74 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>505.92</v>
+        <v>530.67</v>
       </c>
       <c r="F17" t="n">
         <v>99.8</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:35:24.755959+00:00</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>increase toward target 21% of capital (satellite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CRDO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>satellite</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="n">
+        <v>157.49</v>
+      </c>
+      <c r="F18" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-09-15T13:35:23.136618+00:00</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>2026-09-16T13:35:24.965917+00:00</t>
         </is>
       </c>
-      <c r="J17" t="n">
-        <v>518.8150000000001</v>
-      </c>
-      <c r="K17" t="n">
-        <v>12.89500000000004</v>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:35:24.755959+00:00</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>166.67</v>
+      </c>
+      <c r="K18" t="n">
+        <v>36.71999999999991</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>increase toward target 21% of capital (satellite)</t>
         </is>

--- a/trade_journal.xlsx
+++ b/trade_journal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1054,12 +1054,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>satellite</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1068,37 +1068,45 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>188.9875</v>
+        <v>157.49</v>
       </c>
       <c r="F13" t="n">
-        <v>76.2</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-12T14:13:57.782108+00:00</t>
-        </is>
+          <t>2026-09-16T13:35:24.965917+00:00</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-17T13:35:24.755959+00:00</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>166.67</v>
       </c>
       <c r="K13" t="n">
-        <v>-11.61000000000004</v>
+        <v>36.71999999999991</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>increase toward target 18% of capital (core)</t>
+          <t>increase toward target 21% of capital (satellite)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1112,13 +1120,13 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>289.695</v>
+        <v>188.815</v>
       </c>
       <c r="F14" t="n">
-        <v>71.3</v>
+        <v>76.2</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1127,27 +1135,27 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-09-11T13:35:24.747298+00:00</t>
+          <t>2026-08-12T14:13:57.782108+00:00</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>-2.464999999999975</v>
+        <v>-11.61000000000004</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>increase toward target 19% of capital (core)</t>
+          <t>increase toward target 18% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>satellite</t>
+          <t>core</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1156,13 +1164,13 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>87.02</v>
+        <v>286.9075</v>
       </c>
       <c r="F15" t="n">
-        <v>100</v>
+        <v>71.3</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1171,22 +1179,22 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-15T13:35:23.136618+00:00</t>
+          <t>2026-09-11T13:35:24.747298+00:00</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>1.570000000000022</v>
+        <v>-2.464999999999975</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>increase toward target 21% of capital (satellite)</t>
+          <t>increase toward target 19% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1200,13 +1208,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>226.705</v>
+        <v>88.03749999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1215,11 +1223,11 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-16T13:35:24.965917+00:00</t>
+          <t>2026-09-15T13:35:23.136618+00:00</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>17.16499999999999</v>
+        <v>1.570000000000022</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1230,7 +1238,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1244,10 +1252,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>530.67</v>
+        <v>230.9166666666667</v>
       </c>
       <c r="F17" t="n">
         <v>99.8</v>
@@ -1259,8 +1267,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:24.755959+00:00</t>
-        </is>
+          <t>2026-09-16T13:35:24.965917+00:00</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>17.16499999999999</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1271,7 +1282,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1285,36 +1296,77 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>157.49</v>
+        <v>294.48</v>
       </c>
       <c r="F18" t="n">
-        <v>99.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:35:24.180017+00:00</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>increase toward target 21% of capital (satellite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>satellite</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>530.67</v>
+      </c>
+      <c r="F19" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-09-16T13:35:24.965917+00:00</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>2026-09-17T13:35:24.755959+00:00</t>
         </is>
       </c>
-      <c r="J18" t="n">
-        <v>166.67</v>
-      </c>
-      <c r="K18" t="n">
-        <v>36.71999999999991</v>
-      </c>
-      <c r="L18" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:35:24.180017+00:00</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>549.4525</v>
+      </c>
+      <c r="K19" t="n">
+        <v>18.78250000000003</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>increase toward target 21% of capital (satellite)</t>
         </is>

--- a/trade_journal.xlsx
+++ b/trade_journal.xlsx
@@ -1106,12 +1106,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>core</t>
+          <t>satellite</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1120,37 +1120,45 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>188.815</v>
+        <v>530.67</v>
       </c>
       <c r="F14" t="n">
-        <v>76.2</v>
+        <v>99.8</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSED</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-12T14:13:57.782108+00:00</t>
-        </is>
+          <t>2026-09-17T13:35:24.755959+00:00</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-18T13:35:24.180017+00:00</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>549.4525</v>
       </c>
       <c r="K14" t="n">
-        <v>-11.61000000000004</v>
+        <v>18.78250000000003</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>increase toward target 18% of capital (core)</t>
+          <t>increase toward target 21% of capital (satellite)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>XLK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1167,10 +1175,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>286.9075</v>
+        <v>188.815</v>
       </c>
       <c r="F15" t="n">
-        <v>71.3</v>
+        <v>76.2</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1179,27 +1187,27 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-09-11T13:35:24.747298+00:00</t>
+          <t>2026-08-12T14:13:57.782108+00:00</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>-2.464999999999975</v>
+        <v>-9.175000000000068</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>increase toward target 19% of capital (core)</t>
+          <t>increase toward target 18% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>satellite</t>
+          <t>core</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1208,13 +1216,13 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>88.03749999999999</v>
+        <v>286.9075</v>
       </c>
       <c r="F16" t="n">
-        <v>100</v>
+        <v>71.3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1223,22 +1231,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-09-15T13:35:23.136618+00:00</t>
+          <t>2026-09-11T13:35:24.747298+00:00</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1.570000000000022</v>
+        <v>-3.972500000000025</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>increase toward target 21% of capital (satellite)</t>
+          <t>increase toward target 19% of capital (core)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>AEHR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1252,13 +1260,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>230.9166666666667</v>
+        <v>88.03749999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>99.8</v>
+        <v>100</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1267,11 +1275,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-16T13:35:24.965917+00:00</t>
+          <t>2026-09-15T13:35:23.136618+00:00</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>17.16499999999999</v>
+        <v>15.61180000000004</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1282,7 +1290,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1299,10 +1307,10 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>294.48</v>
+        <v>230.9166666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>99.7</v>
+        <v>99.8</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1311,8 +1319,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-18T13:35:24.180017+00:00</t>
-        </is>
+          <t>2026-09-16T13:35:24.965917+00:00</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>34.68533333333335</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1323,7 +1334,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1340,31 +1351,23 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>530.67</v>
+        <v>294.48</v>
       </c>
       <c r="F19" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-09-17T13:35:24.755959+00:00</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
           <t>2026-09-18T13:35:24.180017+00:00</t>
         </is>
       </c>
-      <c r="J19" t="n">
-        <v>549.4525</v>
-      </c>
       <c r="K19" t="n">
-        <v>18.78250000000003</v>
+        <v>18.58999999999997</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>

--- a/trade_journal.xlsx
+++ b/trade_journal.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1172,10 +1172,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
-        <v>188.815</v>
+        <v>186.5725</v>
       </c>
       <c r="F15" t="n">
         <v>76.2</v>
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>286.9075</v>
+        <v>279.8225</v>
       </c>
       <c r="F16" t="n">
         <v>71.3</v>
@@ -1246,7 +1246,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AEHR</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1260,13 +1260,13 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>88.03749999999999</v>
+        <v>523.49</v>
       </c>
       <c r="F17" t="n">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1275,11 +1275,8 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-09-15T13:35:23.136618+00:00</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>15.61180000000004</v>
+          <t>2026-10-26T13:35:25.525115+00:00</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1290,7 +1287,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>ASX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1304,13 +1301,13 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>230.9166666666667</v>
+        <v>38.87</v>
       </c>
       <c r="F18" t="n">
-        <v>99.8</v>
+        <v>75</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1319,11 +1316,8 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-09-16T13:35:24.965917+00:00</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>34.68533333333335</v>
+          <t>2026-10-26T13:35:25.525115+00:00</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1334,7 +1328,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1351,25 +1345,178 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
+        <v>893.3629</v>
+      </c>
+      <c r="F19" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-10-26T13:35:25.525115+00:00</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>increase toward target 21% of capital (satellite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AEHR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>satellite</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>88.03749999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>100</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-09-15T13:35:23.136618+00:00</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-10-26T13:35:25.525115+00:00</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-189.5131999999999</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>increase toward target 21% of capital (satellite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ALAB</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>satellite</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
         <v>294.48</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F21" t="n">
         <v>99.7</v>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t>2026-09-18T13:35:24.180017+00:00</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>18.58999999999997</v>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-10-26T13:35:25.525115+00:00</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>258.44608</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-17.44392000000005</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>increase toward target 21% of capital (satellite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>satellite</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>230.9166666666667</v>
+      </c>
+      <c r="F22" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-09-16T13:35:24.965917+00:00</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-10-26T13:35:25.525115+00:00</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>227.54</v>
+      </c>
+      <c r="K22" t="n">
+        <v>27.93200000000002</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>increase toward target 21% of capital (satellite)</t>
         </is>
